--- a/panchang-data/Vancouver_BC2026.xlsx
+++ b/panchang-data/Vancouver_BC2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5409">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16252,6 +16252,9 @@
   </si>
   <si>
     <t>121°03'06.38</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16741,7 +16744,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16827,7 +16830,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16913,7 +16916,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16999,7 +17002,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>88</v>
@@ -17085,7 +17088,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>106</v>
@@ -17171,7 +17174,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>124</v>
@@ -17257,7 +17260,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>142</v>
@@ -17343,7 +17346,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17429,7 +17432,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17515,7 +17518,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17601,7 +17604,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>88</v>
@@ -17687,7 +17690,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>106</v>
@@ -17773,7 +17776,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>124</v>
@@ -17859,7 +17862,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>142</v>
@@ -17945,7 +17948,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -18031,7 +18034,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18117,7 +18120,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18203,7 +18206,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>88</v>
@@ -18289,7 +18292,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>106</v>
@@ -18375,7 +18378,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>124</v>
@@ -18461,7 +18464,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>142</v>
@@ -18547,7 +18550,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18633,7 +18636,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18719,7 +18722,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18805,7 +18808,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>88</v>
@@ -18891,7 +18894,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>106</v>
@@ -18977,7 +18980,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>124</v>
@@ -19063,7 +19066,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>142</v>
@@ -19149,7 +19152,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19235,7 +19238,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19321,7 +19324,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19407,7 +19410,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>69</v>
+        <v>567</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>88</v>
@@ -19493,7 +19496,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>106</v>
@@ -19579,7 +19582,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>124</v>
@@ -19665,7 +19668,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>142</v>
@@ -19751,7 +19754,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19837,7 +19840,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19923,7 +19926,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -20009,7 +20012,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>88</v>
@@ -20095,7 +20098,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>106</v>
@@ -20181,7 +20184,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>124</v>
@@ -20267,7 +20270,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>142</v>
@@ -20353,7 +20356,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20439,7 +20442,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20525,7 +20528,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20611,7 +20614,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>88</v>
@@ -20697,7 +20700,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>106</v>
@@ -20783,7 +20786,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>124</v>
@@ -20869,7 +20872,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>142</v>
@@ -20955,7 +20958,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21041,7 +21044,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21127,7 +21130,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21213,7 +21216,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>88</v>
@@ -21299,7 +21302,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>106</v>
@@ -21385,7 +21388,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>124</v>
@@ -21471,7 +21474,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>142</v>
@@ -21557,7 +21560,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21643,7 +21646,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21729,7 +21732,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21815,7 +21818,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>88</v>
@@ -21901,7 +21904,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>567</v>
+        <v>997</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>106</v>
@@ -21987,7 +21990,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>124</v>
@@ -22073,7 +22076,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>142</v>
@@ -22159,7 +22162,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22245,7 +22248,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22331,7 +22334,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22417,7 +22420,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>88</v>
@@ -22503,7 +22506,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>106</v>
@@ -22589,7 +22592,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>124</v>
@@ -22675,7 +22678,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>142</v>
@@ -22761,7 +22764,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22847,7 +22850,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22933,7 +22936,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -23019,7 +23022,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>88</v>
@@ -23105,7 +23108,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>106</v>
@@ -23191,7 +23194,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>124</v>
@@ -23277,7 +23280,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>142</v>
@@ -23363,7 +23366,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23449,7 +23452,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23535,7 +23538,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23621,7 +23624,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>88</v>
@@ -23707,7 +23710,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>106</v>
@@ -23793,7 +23796,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>124</v>
@@ -23879,7 +23882,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>142</v>
@@ -23965,7 +23968,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24051,7 +24054,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24137,7 +24140,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24223,7 +24226,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>88</v>
@@ -24309,7 +24312,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>106</v>
@@ -24395,7 +24398,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>124</v>
@@ -24481,7 +24484,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>997</v>
+        <v>1437</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>142</v>
@@ -24567,7 +24570,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24653,7 +24656,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24739,7 +24742,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24825,7 +24828,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>88</v>
@@ -24911,7 +24914,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>106</v>
@@ -24997,7 +25000,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>124</v>
@@ -25083,7 +25086,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>142</v>
@@ -25169,7 +25172,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25255,7 +25258,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25341,7 +25344,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25427,7 +25430,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>88</v>
@@ -25513,7 +25516,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>106</v>
@@ -25599,7 +25602,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>124</v>
@@ -25685,7 +25688,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>142</v>
@@ -25771,7 +25774,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25857,7 +25860,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25943,7 +25946,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -26029,7 +26032,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>88</v>
@@ -26115,7 +26118,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>106</v>
@@ -26201,7 +26204,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>124</v>
@@ -26287,7 +26290,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>142</v>
@@ -26373,7 +26376,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26459,7 +26462,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26545,7 +26548,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26631,7 +26634,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>88</v>
@@ -26717,7 +26720,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>106</v>
@@ -26803,7 +26806,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>124</v>
@@ -26889,7 +26892,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>142</v>
@@ -26975,7 +26978,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27061,7 +27064,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1437</v>
+        <v>1875</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27147,7 +27150,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1875</v>
+        <v>2298</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27233,7 +27236,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1875</v>
+        <v>2298</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>88</v>
@@ -27319,7 +27322,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1875</v>
+        <v>2298</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>106</v>
@@ -27405,7 +27408,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1875</v>
+        <v>2298</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>124</v>
@@ -27491,7 +27494,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1875</v>
+        <v>2298</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>142</v>
@@ -27577,7 +27580,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1875</v>
+        <v>2298</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27663,7 +27666,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1875</v>
+        <v>2298</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27749,7 +27752,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1875</v>
+        <v>2298</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27835,7 +27838,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1875</v>
+        <v>2298</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>88</v>
@@ -27921,7 +27924,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1875</v>
+        <v>2298</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>106</v>
@@ -28007,7 +28010,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1875</v>
+        <v>2298</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>124</v>
@@ -28093,7 +28096,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1875</v>
+        <v>2298</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>142</v>
@@ -28179,7 +28182,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1875</v>
+        <v>2298</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28265,7 +28268,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1875</v>
+        <v>2298</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28351,7 +28354,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1875</v>
+        <v>2298</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28437,7 +28440,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1875</v>
+        <v>5408</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>88</v>
@@ -28523,7 +28526,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1875</v>
+        <v>5408</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>106</v>
@@ -28609,7 +28612,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1875</v>
+        <v>5408</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>124</v>
@@ -28695,7 +28698,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1875</v>
+        <v>5408</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>142</v>
@@ -28781,7 +28784,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1875</v>
+        <v>5408</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28867,7 +28870,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1875</v>
+        <v>5408</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28953,7 +28956,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1875</v>
+        <v>5408</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -29039,7 +29042,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1875</v>
+        <v>5408</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>88</v>
@@ -29125,7 +29128,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1875</v>
+        <v>5408</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>106</v>
@@ -29211,7 +29214,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1875</v>
+        <v>5408</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>124</v>
@@ -29297,7 +29300,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1875</v>
+        <v>5408</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>142</v>
@@ -29383,7 +29386,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1875</v>
+        <v>5408</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29469,7 +29472,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1875</v>
+        <v>5408</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29555,7 +29558,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1875</v>
+        <v>5408</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29641,7 +29644,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>2298</v>
+        <v>5408</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>88</v>
@@ -29727,7 +29730,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2298</v>
+        <v>5408</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>106</v>
@@ -29813,7 +29816,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2298</v>
+        <v>5408</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>124</v>
@@ -29899,7 +29902,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2298</v>
+        <v>5408</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>142</v>
@@ -29985,7 +29988,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2298</v>
+        <v>5408</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30071,7 +30074,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2298</v>
+        <v>5408</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30157,7 +30160,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2298</v>
+        <v>5408</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30243,7 +30246,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2298</v>
+        <v>5408</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>88</v>
@@ -30329,7 +30332,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2298</v>
+        <v>5408</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>106</v>
@@ -30415,7 +30418,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2298</v>
+        <v>5408</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>124</v>
@@ -30501,7 +30504,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2298</v>
+        <v>5408</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>142</v>
@@ -30587,7 +30590,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2298</v>
+        <v>5408</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30673,7 +30676,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2298</v>
+        <v>5408</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30759,7 +30762,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2298</v>
+        <v>5408</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30845,7 +30848,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2298</v>
+        <v>5408</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>88</v>
